--- a/data/interim/law_parsing/labor/legal_frames_review.xlsx
+++ b/data/interim/law_parsing/labor/legal_frames_review.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:AH48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,17 +436,167 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>candidate_id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>source_unit_id</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>doc_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>doc_code</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>unit_ref_full</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>source_ref</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>heading</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>parent_context</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>source_text</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>frame_type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>chu_the</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>vai_tro_chu_the</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hanh_vi</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>doi_tuong_hanh_vi</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>tinh_chat_phap_ly</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>dieu_kien_dinh_luong</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>nguong_ty_le</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>khoang_gia_tri</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>co_quan_tiep_nhan</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>co_quan_xu_ly</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>ket_qua_thu_tuc</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>thoi_han_so</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>don_vi_thoi_han</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>moc_tinh_thoi_han</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>ngoai_le</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>van_ban_dan_chieu</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>ghi_chu_giai_thich</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>muc_do_day_du</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>can_tach_them</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>ly_do_can_tach</t>
         </is>
       </c>
     </row>
@@ -458,17 +608,144 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_THOI_HAN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>khung_nghia_vu</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>kể từ ngày bắt đầu thương lượng</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ngoai_le; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>co_ngoai_le_rieng</t>
         </is>
       </c>
     </row>
@@ -480,17 +757,136 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_NGOAI_LE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>khung_ngoai_le</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>thời gian tham gia các phiên họp không tính vào thời gian</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>quy định tại khoản 2 Điều 176 của Bộ luật này</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ngoai_le; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>co_ngoai_le_rieng</t>
         </is>
       </c>
     </row>
@@ -502,17 +898,144 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_NGOAI_LE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>khung_nghia_vu</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>kể từ ngày bắt đầu thương lượng</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ngoai_le; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>co_ngoai_le_rieng</t>
         </is>
       </c>
     </row>
@@ -524,17 +1047,144 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_THOI_HAN</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>khung_nghia_vu</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>quá 90 ngày</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>kể từ ngày bắt đầu thương lượng</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ngoai_le; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>co_ngoai_le_rieng</t>
         </is>
       </c>
     </row>
@@ -546,17 +1196,136 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_CAM</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>thời gian tham gia các phiên họp không tính vào thời gian</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>quy định tại khoản 2 Điều 176 của Bộ luật này</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=dieu_kien_ap_dung; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>co_ngoai_le_rieng</t>
         </is>
       </c>
     </row>
@@ -568,19 +1337,114 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>CAND_DOC_D70_K2_CAM</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>luat_lao_dong_45_2019_QH14</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Điều 70 khoản 2</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>unit=UNIT_LUAT_LAO_DONG_45_201_D70_K2_S1_SS1|doc_id=DOC_LABOR_08|chapter=V|section=2|article=70|clause=2|point=|lines=468-469</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Điều 70. Quy trình thương lượng tập thể tại doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Chương V | Mục 2 | Điều 70</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Thời gian thương lượng tập thể không được quá 90 ngày kể từ ngày bắt đầu thương lượng, trừ trường hợp các bên có thỏa thuận khác.
+Thời gian tham gia các phiên họp thương lượng tập thể của đại diện bên người lao động được tính là thời gian làm việc có hưởng lương. Trường hợp người lao động là thành viên của tổ chức đại diện người lao động tham gia các phiên họp thương lượng tập thể thì thời gian tham gia các phiên họp không tính vào thời gian quy định tại khoản 2 Điều 176 của Bộ luật này.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>khung_ngoai_le</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>áp dụng quy định loại trừ</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>trừ trường hợp các bên có thỏa thuận khác</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>bo_sung_ngoai_le_tu_van_ban_goc;tach_frame_ngoai_le</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -590,19 +1454,114 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>CAND_DOC_D4_K3_HO_SO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D4_K3_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Điều 4 khoản 3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D4_K3_S1_SS1|doc_id=DOC_LABOR_09|chapter=II|section=|article=4|clause=3|point=|lines=46-47</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Điều 4. Báo cáo sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng, trước ngày 15 tháng 6 và hằng năm, trước ngày 15 tháng 12, Sở Lao động - Thương binh và Xã hội có trách nhiệm báo cáo Bộ Lao động - Thương binh và Xã hội về tình hình sử dụng lao động trên địa bàn thông qua Cổng Dịch vụ công Quốc gia theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.
+Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Ph</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -612,19 +1571,114 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>CAND_DOC_D4_K3_HO_SO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D4_K3_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Điều 4 khoản 3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D4_K3_S1_SS1|doc_id=DOC_LABOR_09|chapter=II|section=|article=4|clause=3|point=|lines=46-47</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Điều 4. Báo cáo sử dụng lao động</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng, trước ngày 15 tháng 6 và hằng năm, trước ngày 15 tháng 12, Sở Lao động - Thương binh và Xã hội có trách nhiệm báo cáo Bộ Lao động - Thương binh và Xã hội về tình hình sử dụng lao động trên địa bàn thông qua Cổng Dịch vụ công Quốc gia theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.
+Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Trường hợp Sở Lao động - Thương binh và Xã hội không thể báo cáo tình hình sử dụng lao động thông qua Cổng Dịch vụ công Quốc gia thì gửi báo cáo bằng bản giấy đến Bộ Lao động - Thương binh và Xã hội theo Mẫu số 02/PLI Ph</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -634,15 +1688,125 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>CAND_DOC_D6_NGUONG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D6_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Điều 6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D6_S1_SS1|doc_id=DOC_LABOR_09|chapter=III|section=1|article=6|clause=|point=|lines=76-77</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Điều 6. Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>khung_nguong_dinh_luong</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>vốn điều lệ</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện .</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở x</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>specialized_frame_slot_ok; candidate_type=nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -652,15 +1816,125 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>CAND_DOC_D6_NGUONG</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D6_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Điều 6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D6_S1_SS1|doc_id=DOC_LABOR_09|chapter=III|section=1|article=6|clause=|point=|lines=76-77</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Điều 6. Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nội dung hợp đồng lao động đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện theo quy định tại khoản 1 Điều 21 của Bộ luật Lao động.</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>khung_nguong_dinh_luong</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>vốn điều lệ</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>đối với người lao động được thuê làm giám đốc trong doanh nghiệp do Nhà nước nắm giữ từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở xuống thực hiện .</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>từ 50% vốn điều lệ hoặc tổng số cổ phần có quyền biểu quyết trở x</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>specialized_frame_slot_ok; candidate_type=nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -670,19 +1944,129 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>CAND_DOC_D20_K1_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D20_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D20_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=20|clause=1|point=|lines=193-193</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Điều 20. Nộp bổ sung tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Trong thời hạn 30 ngày kể từ ngày rút tiền ký quỹ để thanh toán đối với trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại phải nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>khung_nghia_vu</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>chu_the_bi_dieu_chinh</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>nộp bổ sung tiền ký quỹ bảo đảm</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>nộp bổ</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=nghia_vu</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -692,15 +2076,121 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>CAND_DOC_D20_K1_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D20_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Điều 20 khoản 1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D20_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=2|article=20|clause=1|point=|lines=193-193</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Điều 20. Nộp bổ sung tiền ký quỹ</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 2 | Điều 20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Trong thời hạn 30 ngày kể từ ngày rút tiền ký quỹ để thanh toán đối với trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại phải nộp bổ sung tiền ký quỹ bảo đảm quy định tại khoản 2 Điều 21 Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>trường hợp quy định tại các điểm a và điểm b khoản 1 Điều 18 và Điều 19 Nghị định này, doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>ngay</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>specialized_frame_slot_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>thieu_vai_slot</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -710,19 +2200,109 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>CAND_DOC_D23_K2_HO_SO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D23_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Điều 23 khoản 2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D23_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=23|clause=2|point=|lines=206-206</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Điều 23. Giấy phép hoạt động cho thuê lại lao động</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 23</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -732,19 +2312,109 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>CAND_DOC_D23_K2_HO_SO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D23_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Điều 23 khoản 2</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D23_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=23|clause=2|point=|lines=206-206</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Điều 23. Giấy phép hoạt động cho thuê lại lao động</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 23</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Nội dung giấy phép hoạt động cho thuê lại lao động theo Mẫu số 04/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -754,19 +2424,109 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>CAND_DOC_D24_K2_HO_SO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D24_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=2|point=|lines=213-213</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -776,19 +2536,109 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>CAND_DOC_D24_K2_HO_SO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D24_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=2|point=|lines=213-213</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bản lý lịch tự thuật của người đại diện theo pháp luật của doanh nghiệp theo Mẫu số 07/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -798,19 +2648,109 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>CAND_DOC_D24_K5_HO_SO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D24_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=5|point=|lines=220-220</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -820,19 +2760,109 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>CAND_DOC_D24_K5_HO_SO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D24_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Điều 24 khoản 5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D24_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=24|clause=5|point=|lines=220-220</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Điều 24. Hồ sơ đề nghị cấp giấy phép</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 24</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Giấy chứng nhận tiền ký quỹ hoạt động cho thuê lại lao động theo Mẫu số 01/PLIII Phụ lục III ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -842,17 +2872,111 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>CAND_DOC_D26_K2_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D26_K2_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D26_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=26|clause=2|point=a|lines=239-239</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Điều 26. Gia hạn giấy phép</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 26</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -864,17 +2988,111 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>CAND_DOC_D26_K2_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D26_K2_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Điều 26 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D26_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=26|clause=2|point=a|lines=239-239</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Điều 26. Gia hạn giấy phép</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 26</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị gia hạn giấy phép của doanh nghiệp theo Mẫu số 05/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -886,19 +3104,117 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K1_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=1|point=|lines=280-280</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại bị thu hồi giấy phép trong các trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép trong các</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -908,19 +3224,117 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K1_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=1|point=|lines=280-280</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại bị thu hồi giấy phép trong các trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>thu hồi giấy phép trong các</t>
         </is>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây:</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>trường hợp sau đây</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép trong các</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr"/>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -930,17 +3344,119 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K2_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K2_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>co_the</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -952,17 +3468,119 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K2_A_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K2_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>co_the</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -974,17 +3592,119 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K2_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K2_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm a</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_A_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=a|lines=282-282</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Văn bản đề nghị thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Nghị định</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>thu hồi giấy phép theo Mẫu số 06/PLIII Phụ lục III ban hành kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -996,17 +3716,111 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K2_C_HO_SO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K2_C_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm c</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_C_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=c|lines=284-284</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1018,17 +3832,111 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K2_C_HO_SO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K2_C_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 2 điểm c</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K2_C_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=2|point=c|lines=284-284</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Báo cáo tình hình hoạt động cho thuê lại lao động của doanh nghiệp theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này;</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1040,19 +3948,145 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K5_THOI_HAN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>khung_thoi_han</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>chu_the_bi_dieu_chinh</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>cấp giấy phép</t>
         </is>
       </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>nam</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thoi_han</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>rat_day_du</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1062,19 +4096,145 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K5_CAM</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>khung_nguong_dinh_luong</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>cấp giấy phép</t>
         </is>
       </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>nam</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=nguong_so_luong</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>rat_day_du</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1084,19 +4244,145 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K5_THOI_HAN</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>cấp giấy phép</t>
         </is>
       </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>nam</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>rat_day_du</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1106,19 +4392,145 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K5_THOI_HAN</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D28_K5_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 5</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D28_K5_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=3|article=28|clause=5|point=|lines=294-294</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Điều 28. Thu hồi giấy phép</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 3 | Điều 28</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Doanh nghiệp cho thuê lại không được cấp giấy phép trong thời hạn 05 năm, kể từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và điểm e khoản 1 Điều này.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>khung_ket_qua_phap_ly</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>chu_the_bi_dieu_chinh</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>cấp giấy phép</t>
         </is>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>thời hạn 05 năm</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>bi_cam</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>từ ngày bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>bị thu hồi giấy phép vì vi phạm các nội dung quy định tại các điểm c, d, đ và</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>nam</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>ke_tu_moc_tham_chieu</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>khoản 1</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=ket_qua_phap_ly</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>rat_day_du</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1128,17 +4540,115 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>CAND_DOC_D31_K2_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D31_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Điều 31 khoản 2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D31_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=4|article=31|clause=2|point=|lines=302-302</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 4 | Điều 31</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng và hằng năm, báo cáo tình hình hoạt động cho thuê lại lao động theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao động trên địa bàn đó đối với trường hợp doanh nghiệp cho thuê lại sang địa bàn cấp tỉnh khác hoạt động. Báo cáo 06 tháng gửi trước ngày 20 tháng 6 và báo cáo năm gửi trước ngày 20 tháng 12.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr"/>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr"/>
+      <c r="AB33" t="inlineStr"/>
+      <c r="AC33" t="inlineStr"/>
+      <c r="AD33" t="inlineStr"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi;co_nhieu_ket_qua</t>
         </is>
       </c>
     </row>
@@ -1150,17 +4660,115 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
+          <t>CAND_DOC_D31_K2_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D31_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Điều 31 khoản 2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D31_K2_S1_SS1|doc_id=DOC_LABOR_09|chapter=IV|section=4|article=31|clause=2|point=|lines=302-302</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Điều 31. Trách nhiệm của doanh nghiệp cho thuê lại</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 4 | Điều 31</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Định kỳ 06 tháng và hằng năm, báo cáo tình hình hoạt động cho thuê lại lao động theo Mẫu số 09/PLIII Phụ lục III ban hành kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao động trên địa bàn đó đối với trường hợp doanh nghiệp cho thuê lại sang địa bàn cấp tỉnh khác hoạt động. Báo cáo 06 tháng gửi trước ngày 20 tháng 6 và báo cáo năm gửi trước ngày 20 tháng 12.</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>trường hợp doanh nghiệp cho thuê lại sang địa bàn</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này, gửi Chủ tịch Ủy ban nhân dân cấp tỉnh, Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đặt trụ sở chính; đồng thời báo cáo Sở Lao động - Thương binh và Xã hội nơi doanh nghiệp đến hoạt động cho thuê lại lao động về tình hình hoạt động cho thuê lại lao</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
+      <c r="AC34" t="inlineStr"/>
+      <c r="AD34" t="inlineStr"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi;co_nhieu_ket_qua</t>
         </is>
       </c>
     </row>
@@ -1172,19 +4780,109 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
+          <t>CAND_DOC_D85_K1_HO_SO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D85_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Điều 85 khoản 1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D85_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IX|section=3|article=85|clause=1|point=|lines=776-776</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Điều 85. Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục tại nơi làm việc</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Chương IX | Mục 3 | Điều 85</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau:</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr"/>
+      <c r="AC35" t="inlineStr"/>
+      <c r="AD35" t="inlineStr"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1194,19 +4892,109 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>CAND_DOC_D85_K1_HO_SO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNIT_145_2020_N_CP_D85_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_09</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>145/2020/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Điều 85 khoản 1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>unit=UNIT_145_2020_N_CP_D85_K1_S1_SS1|doc_id=DOC_LABOR_09|chapter=IX|section=3|article=85|clause=1|point=|lines=776-776</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Điều 85. Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục tại nơi làm việc</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Chương IX | Mục 3 | Điều 85</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Quy định của người sử dụng lao động về phòng, chống quấy rối tình dục trong nội quy lao động hoặc bằng phụ lục ban hành kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau:</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>kèm theo nội quy lao động, bao gồm các nội dung cơ bản sau</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr"/>
+      <c r="AB36" t="inlineStr"/>
+      <c r="AC36" t="inlineStr"/>
+      <c r="AD36" t="inlineStr"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1216,15 +5004,117 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
+          <t>CAND_DOC_D17_K2_DANG_KY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_10</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Điều 17 khoản 2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1|doc_id=DOC_LABOR_10|chapter=II|section=2|article=17|clause=2|point=|lines=199-199</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Điều 17. Quyền hạn của cơ quan bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Chương II | Mục 2 | Điều 17</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Được cơ quan đăng ký kinh doanh, cơ quan cấp giấy chứng nhận hoạt động hoặc giấy phép hoạt động kết nối, chia sẻ thông tin hoặc cung cấp bản sao giấy phép hoạt động, giấy chứng nhận hoạt động hoặc giấy chứng nhận đăng ký doanh nghiệp, hợp tác xã, hộ kinh doanh để rà soát, kiểm tra việc thực hiện đăng ký tham gia bảo hiểm xã hội bắt buộc đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr"/>
+      <c r="AB37" t="inlineStr"/>
+      <c r="AC37" t="inlineStr"/>
+      <c r="AD37" t="inlineStr"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>specialized_frame_slot_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1234,15 +5124,117 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
+          <t>CAND_DOC_D17_K2_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_10</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Điều 17 khoản 2</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D17_K2_S1_SS1|doc_id=DOC_LABOR_10|chapter=II|section=2|article=17|clause=2|point=|lines=199-199</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Điều 17. Quyền hạn của cơ quan bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Chương II | Mục 2 | Điều 17</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Được cơ quan đăng ký kinh doanh, cơ quan cấp giấy chứng nhận hoạt động hoặc giấy phép hoạt động kết nối, chia sẻ thông tin hoặc cung cấp bản sao giấy phép hoạt động, giấy chứng nhận hoạt động hoặc giấy chứng nhận đăng ký doanh nghiệp, hợp tác xã, hộ kinh doanh để rà soát, kiểm tra việc thực hiện đăng ký tham gia bảo hiểm xã hội bắt buộc đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>giấy chứng nhận đăng ký doanh nghiệp</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>duoc_phep</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>đối với doanh nghiệp, tổ chức thành lập mới.</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr"/>
+      <c r="AB38" t="inlineStr"/>
+      <c r="AC38" t="inlineStr"/>
+      <c r="AD38" t="inlineStr"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>specialized_frame_slot_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1252,17 +5244,119 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
+          <t>CAND_DOC_D27_K1_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_10</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 1 điểm a</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1|doc_id=DOC_LABOR_10|chapter=IV|section=1|article=27|clause=1|point=a|lines=293-293</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Điều 27. Hồ sơ đăng ký tham gia bảo hiểm xã hội bắt buộc và bảo hiểm xã hội tự nguyện</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 1 | Điều 27</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động kèm theo danh sách người lao động tham gia bảo hiểm xã hội;</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+      <c r="AC39" t="inlineStr"/>
+      <c r="AD39" t="inlineStr"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1274,17 +5368,119 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>CAND_DOC_D27_K1_A_HO_SO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_10</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>bao_hiem_xa_hoi_41_2024_QH15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Điều 27 khoản 1 điểm a</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>unit=UNIT_BAO_HIEM_XA_HOI_41_2_D27_K1_A_S1_SS1|doc_id=DOC_LABOR_10|chapter=IV|section=1|article=27|clause=1|point=a|lines=293-293</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Điều 27. Hồ sơ đăng ký tham gia bảo hiểm xã hội bắt buộc và bảo hiểm xã hội tự nguyện</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Chương IV | Mục 1 | Điều 27</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Tờ khai đăng ký tham gia bảo hiểm xã hội của người sử dụng lao động kèm theo danh sách người lao động tham gia bảo hiểm xã hội;</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>danh sách</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>danh sách người lao động tham gia bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr"/>
+      <c r="AB40" t="inlineStr"/>
+      <c r="AC40" t="inlineStr"/>
+      <c r="AD40" t="inlineStr"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1296,17 +5492,132 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
+          <t>CAND_DOC_D10_K4_B_HO_SO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D10_K4_B_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Điều 10 khoản 4 điểm b</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D10_K4_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=II|section=|article=10|clause=4|point=b|lines=99-100</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Điều 10. Tạm dừng đóng vào quỹ hưu trí và tử tuất theo quy định tại khoản 1 và khoản 3 Điều 37 của Luật Bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc.
+Người sử dụng lao động thuộc đối tượng quy định tại điểm b khoản 2 Điều này bị thiệt hại trên 50% tổng giá trị tài sản, làm văn bản đề nghị kèm theo Báo cáo kiểm kê tài sản gần nhất trước thời điểm bị thiệt hại; Biên bản kiểm kê tài sản bị thiệt hại do thiên tai, hoả hoạn, dịch bệnh, mất mùa. Trường hợp không bố trí được việc làm cho người lao động, trong đó số lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa thì làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc;</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr"/>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="inlineStr"/>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1318,17 +5629,132 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>CAND_DOC_D10_K4_B_HO_SO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D10_K4_B_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Điều 10 khoản 4 điểm b</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D10_K4_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=II|section=|article=10|clause=4|point=b|lines=99-100</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Điều 10. Tạm dừng đóng vào quỹ hưu trí và tử tuất theo quy định tại khoản 1 và khoản 3 Điều 37 của Luật Bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Chương II | Điều 10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Người sử dụng lao động thuộc đối tượng quy định tại điểm a khoản 2 Điều này, làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc.
+Người sử dụng lao động thuộc đối tượng quy định tại điểm b khoản 2 Điều này bị thiệt hại trên 50% tổng giá trị tài sản, làm văn bản đề nghị kèm theo Báo cáo kiểm kê tài sản gần nhất trước thời điểm bị thiệt hại; Biên bản kiểm kê tài sản bị thiệt hại do thiên tai, hoả hoạn, dịch bệnh, mất mùa. Trường hợp không bố trí được việc làm cho người lao động, trong đó số lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa thì làm văn bản đề nghị kèm theo danh sách lao động tại thời điểm trước khi thiên tai, hỏa hoạn, dịch bệnh, mất mùa và tại thời điểm đề nghị; danh sách lao động thuộc đối tượng tham gia bảo hiểm xã hội bắt buộc phải tạm thời nghỉ việc;</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>khi tạm dừng sản xuất, kinh doanh và tại thời điểm đề nghị</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>từ 50% trở lên so với tổng số lao động có mặt trước khi thiên tai</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>danh sách lao động tại thời điểm trước</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr"/>
+      <c r="AB42" t="inlineStr"/>
+      <c r="AC42" t="inlineStr"/>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>khoản 2</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1340,19 +5766,109 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>CAND_DOC_D12_K1_HO_SO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D12_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Điều 12 khoản 1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D12_K1_S1_SS1|doc_id=DOC_LABOR_11|chapter=III|section=1|article=12|clause=1|point=|lines=122-122</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Điều 12. Điều kiện hưởng lương hưu</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 12</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="inlineStr"/>
+      <c r="AD43" t="inlineStr"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1362,19 +5878,109 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
+          <t>CAND_DOC_D12_K1_HO_SO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D12_K1_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Điều 12 khoản 1</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D12_K1_S1_SS1|doc_id=DOC_LABOR_11|chapter=III|section=1|article=12|clause=1|point=|lines=122-122</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Điều 12. Điều kiện hưởng lương hưu</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Chương III | Mục 1 | Điều 12</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Công việc khai thác than trong hầm lò theo Phụ lục I ban hành kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
         </is>
       </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này.</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+      <c r="AC44" t="inlineStr"/>
+      <c r="AD44" t="inlineStr"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>khong</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1384,17 +5990,123 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K1_C_HANH_DONG_CO_QUAN</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D28_K1_C_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1 điểm c</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D28_K1_C_S1_SS1|doc_id=DOC_LABOR_11|chapter=V|section=|article=28|clause=1|point=c|lines=309-309</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Điều 28. Căn cứ xác nhận thời gian đóng bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Chương V | Điều 28</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể đối với trường hợp đang làm thủ tục giải thể;</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>khung_thu_tuc</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>co_quan</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>thủ tục</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr"/>
+      <c r="AB45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr"/>
+      <c r="AD45" t="inlineStr"/>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thu_tuc</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1406,17 +6118,123 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
+          <t>CAND_DOC_D28_K1_C_QUY_TAC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D28_K1_C_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Điều 28 khoản 1 điểm c</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D28_K1_C_S1_SS1|doc_id=DOC_LABOR_11|chapter=V|section=|article=28|clause=1|point=c|lines=309-309</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Điều 28. Căn cứ xác nhận thời gian đóng bảo hiểm xã hội</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Chương V | Điều 28</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Thông báo của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể đối với trường hợp đang làm thủ tục giải thể;</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>khung_dieu_kien</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>cơ quan đăng ký kinh doanh</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>co_quan</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>của cơ quan đăng ký kinh doanh về việc doanh nghiệp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm thủ tục giải thể</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>trường hợp đang làm</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>cơ quan đăng ký kinh doanh</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr"/>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
+      <c r="AD46" t="inlineStr"/>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=dieu_kien_ap_dung</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>day_du</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1428,17 +6246,116 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
+          <t>CAND_DOC_D36_K1_B_HO_SO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D36_K1_B_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Điều 36 khoản 1 điểm b</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D36_K1_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=VI|section=|article=36|clause=1|point=b|lines=408-409</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Điều 36. Hồ sơ đề nghị tính thời gian công tác đối với người lao động đi hợp tác lao động trước ngày 01 tháng 01 năm 1995</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Chương VI | Điều 36</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” của Cục Hợp tác quốc tế về lao động (nay là Cục Quản lý lao động ngoài nước) cấp.
+Trường hợp không còn bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” thì phải có Giấy xác nhận về thời gian đi hợp tác lao động để giải quyết chế độ bảo hiểm xã hội của Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành kèm theo Nghị định này);</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Trường hợp không còn bản chính “</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr"/>
+      <c r="AB47" t="inlineStr"/>
+      <c r="AC47" t="inlineStr"/>
+      <c r="AD47" t="inlineStr"/>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF47" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG47" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
@@ -1450,17 +6367,116 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>CAND_DOC_D36_K1_B_HO_SO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNIT_158_2025_N_CP_D36_K1_B_S1_SS1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>DOC_LABOR_11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>158/2025/NĐ-CP</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Điều 36 khoản 1 điểm b</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>unit=UNIT_158_2025_N_CP_D36_K1_B_S1_SS1|doc_id=DOC_LABOR_11|chapter=VI|section=|article=36|clause=1|point=b|lines=408-409</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Điều 36. Hồ sơ đề nghị tính thời gian công tác đối với người lao động đi hợp tác lao động trước ngày 01 tháng 01 năm 1995</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Chương VI | Điều 36</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” của Cục Hợp tác quốc tế về lao động (nay là Cục Quản lý lao động ngoài nước) cấp.
+Trường hợp không còn bản chính “Thông báo chuyển trả” hoặc “Quyết định chuyển trả” thì phải có Giấy xác nhận về thời gian đi hợp tác lao động để giải quyết chế độ bảo hiểm xã hội của Cục Quản lý lao động ngoài nước trên cơ sở đơn đề nghị của người lao động (theo Mẫu số 01 và số 02 Phụ lục II ban hành kèm theo Nghị định này);</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>khung_ho_so</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>doanh nghiệp</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>chu_the_thuc_hien</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>thành phần hồ sơ</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>bat_buoc</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Trường hợp không còn bản chính “</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr"/>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>kèm theo Nghị định này)</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr"/>
+      <c r="AB48" t="inlineStr"/>
+      <c r="AC48" t="inlineStr"/>
+      <c r="AD48" t="inlineStr"/>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>quality_ok; candidate_type=thanh_phan_ho_so; grounded_on_source_text</t>
+        </is>
+      </c>
+      <c r="AF48" t="inlineStr">
+        <is>
+          <t>kha_day_du</t>
+        </is>
+      </c>
+      <c r="AG48" t="inlineStr">
+        <is>
+          <t>co</t>
+        </is>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>nhieu_hanh_vi</t>
         </is>
       </c>
     </row>
